--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
   <si>
     <t>Filename</t>
   </si>
@@ -820,97 +820,103 @@
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0.9928,0.0011,0.0037,0.0001</t>
   </si>
   <si>
-    <t>0.1598,0.0072,0.0197,0.8642</t>
+    <t>0.1597,0.0072,0.0198,0.8639</t>
   </si>
   <si>
     <t>0.9927,0.0015,0.0017,0.0008</t>
   </si>
   <si>
-    <t>0.6539,0.0026,0.0226,0.1098</t>
-  </si>
-  <si>
-    <t>0.9421,0.0021,0.0288,0.0005</t>
-  </si>
-  <si>
-    <t>0.9318,0.0037,0.0409,0.0008</t>
+    <t>0.6542,0.0026,0.0226,0.1093</t>
+  </si>
+  <si>
+    <t>0.9420,0.0021,0.0289,0.0005</t>
+  </si>
+  <si>
+    <t>0.9317,0.0037,0.0410,0.0008</t>
   </si>
   <si>
     <t>0.9290,0.0012,0.0520,0.0003</t>
   </si>
   <si>
-    <t>0.8249,0.0006,0.1499,0.0003</t>
+    <t>0.8246,0.0006,0.1503,0.0003</t>
   </si>
   <si>
     <t>0.9834,0.0041,0.0065,0.0005</t>
   </si>
   <si>
-    <t>0.9534,0.0038,0.0257,0.0006</t>
-  </si>
-  <si>
-    <t>0.8949,0.0004,0.0982,0.0003</t>
-  </si>
-  <si>
-    <t>0.9485,0.0015,0.0325,0.0002</t>
+    <t>0.9533,0.0038,0.0258,0.0006</t>
+  </si>
+  <si>
+    <t>0.8947,0.0004,0.0985,0.0003</t>
+  </si>
+  <si>
+    <t>0.9484,0.0015,0.0325,0.0002</t>
   </si>
   <si>
     <t>0.9738,0.0021,0.0202,0.0002</t>
   </si>
   <si>
-    <t>0.0898,0.0158,0.9195,0.0013</t>
-  </si>
-  <si>
-    <t>0.8413,0.0003,0.2727,0.0000</t>
-  </si>
-  <si>
-    <t>0.2347,0.0072,0.8023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9569,0.0008,0.0518,0.0001</t>
-  </si>
-  <si>
-    <t>0.0088,0.9836,0.4226,0.0013</t>
-  </si>
-  <si>
-    <t>0.0389,0.9568,0.2944,0.0036</t>
-  </si>
-  <si>
-    <t>0.4177,0.8301,0.0165,0.0001</t>
-  </si>
-  <si>
-    <t>0.0808,0.8738,0.3818,0.0118</t>
-  </si>
-  <si>
-    <t>0.0022,0.9983,0.1742,0.0001</t>
-  </si>
-  <si>
-    <t>0.8845,0.0017,0.1452,0.0006</t>
-  </si>
-  <si>
-    <t>0.5394,0.0051,0.5304,0.0005</t>
-  </si>
-  <si>
-    <t>0.1005,0.0002,0.9600,0.0000</t>
-  </si>
-  <si>
-    <t>0.1281,0.0025,0.9216,0.0002</t>
-  </si>
-  <si>
-    <t>0.1313,0.0018,0.9297,0.0003</t>
-  </si>
-  <si>
-    <t>0.3241,0.0005,0.8278,0.0001</t>
+    <t>0.0896,0.0158,0.9197,0.0013</t>
+  </si>
+  <si>
+    <t>0.8411,0.0003,0.2733,0.0000</t>
+  </si>
+  <si>
+    <t>0.2348,0.0072,0.8023,0.0003</t>
+  </si>
+  <si>
+    <t>0.9569,0.0008,0.0519,0.0001</t>
+  </si>
+  <si>
+    <t>0.0088,0.9836,0.4236,0.0013</t>
+  </si>
+  <si>
+    <t>0.0389,0.9567,0.2951,0.0036</t>
+  </si>
+  <si>
+    <t>0.4177,0.8299,0.0166,0.0001</t>
+  </si>
+  <si>
+    <t>0.0807,0.8736,0.3827,0.0119</t>
+  </si>
+  <si>
+    <t>0.0022,0.9983,0.1746,0.0001</t>
+  </si>
+  <si>
+    <t>0.8844,0.0017,0.1454,0.0006</t>
+  </si>
+  <si>
+    <t>0.5388,0.0051,0.5312,0.0005</t>
+  </si>
+  <si>
+    <t>0.1004,0.0002,0.9601,0.0000</t>
+  </si>
+  <si>
+    <t>0.1281,0.0025,0.9217,0.0002</t>
+  </si>
+  <si>
+    <t>0.1314,0.0018,0.9297,0.0003</t>
+  </si>
+  <si>
+    <t>0.3242,0.0005,0.8278,0.0001</t>
   </si>
   <si>
     <t>0.0169,0.0005,0.9922,0.0001</t>
   </si>
   <si>
-    <t>0.9328,0.0167,0.0381,0.0017</t>
+    <t>0.9328,0.0166,0.0382,0.0017</t>
   </si>
   <si>
     <t>0.9554,0.0258,0.0210,0.0022</t>
@@ -919,58 +925,58 @@
     <t>0.0035,0.0002,0.9982,0.0001</t>
   </si>
   <si>
-    <t>0.0266,0.2056,0.9324,0.0018</t>
-  </si>
-  <si>
-    <t>0.6874,0.0013,0.3356,0.0003</t>
-  </si>
-  <si>
-    <t>0.7086,0.0053,0.2877,0.0010</t>
-  </si>
-  <si>
-    <t>0.8633,0.0838,0.0485,0.0057</t>
-  </si>
-  <si>
-    <t>0.0272,0.7867,0.7326,0.0047</t>
-  </si>
-  <si>
-    <t>0.0007,0.3227,0.9897,0.0001</t>
+    <t>0.0267,0.2050,0.9324,0.0018</t>
+  </si>
+  <si>
+    <t>0.6869,0.0013,0.3363,0.0003</t>
+  </si>
+  <si>
+    <t>0.7082,0.0052,0.2883,0.0010</t>
+  </si>
+  <si>
+    <t>0.8634,0.0836,0.0485,0.0057</t>
+  </si>
+  <si>
+    <t>0.0271,0.7862,0.7332,0.0047</t>
+  </si>
+  <si>
+    <t>0.0007,0.3224,0.9897,0.0001</t>
   </si>
   <si>
     <t>0.0009,0.0020,0.9988,0.0001</t>
   </si>
   <si>
-    <t>0.0190,0.0426,0.9689,0.0005</t>
-  </si>
-  <si>
-    <t>0.6272,0.0007,0.4392,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.4288,0.9922,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.9651,0.1297,0.0035</t>
-  </si>
-  <si>
-    <t>0.0017,0.0284,0.9962,0.0004</t>
-  </si>
-  <si>
-    <t>0.0480,0.3198,0.0469,0.7530</t>
-  </si>
-  <si>
-    <t>0.0006,0.9998,0.0098,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9994,0.2844,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9997,0.1812,0.0000</t>
+    <t>0.0190,0.0425,0.9689,0.0005</t>
+  </si>
+  <si>
+    <t>0.6269,0.0006,0.4398,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.4280,0.9922,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.9650,0.1298,0.0035</t>
+  </si>
+  <si>
+    <t>0.0017,0.0283,0.9962,0.0004</t>
+  </si>
+  <si>
+    <t>0.0483,0.3194,0.0471,0.7524</t>
+  </si>
+  <si>
+    <t>0.0006,0.9998,0.0099,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9994,0.2849,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9997,0.1816,0.0000</t>
   </si>
   <si>
     <t>0.0002,0.0089,0.9993,0.0001</t>
   </si>
   <si>
-    <t>0.0005,0.0603,0.9980,0.0003</t>
+    <t>0.0005,0.0601,0.9980,0.0003</t>
   </si>
   <si>
     <t>0.0084,0.0026,0.9931,0.0003</t>
@@ -979,40 +985,40 @@
     <t>0.1478,0.0001,0.9496,0.0000</t>
   </si>
   <si>
-    <t>0.0258,0.0006,0.9878,0.0000</t>
-  </si>
-  <si>
-    <t>0.0748,0.0057,0.9419,0.0004</t>
-  </si>
-  <si>
-    <t>0.9307,0.0031,0.0544,0.0003</t>
-  </si>
-  <si>
-    <t>0.6888,0.0006,0.3408,0.0002</t>
-  </si>
-  <si>
-    <t>0.8650,0.0084,0.0689,0.0013</t>
+    <t>0.0258,0.0006,0.9879,0.0000</t>
+  </si>
+  <si>
+    <t>0.0748,0.0057,0.9420,0.0004</t>
+  </si>
+  <si>
+    <t>0.9306,0.0031,0.0545,0.0003</t>
+  </si>
+  <si>
+    <t>0.6885,0.0006,0.3413,0.0001</t>
+  </si>
+  <si>
+    <t>0.8648,0.0084,0.0690,0.0013</t>
   </si>
   <si>
     <t>0.0714,0.0016,0.9401,0.0002</t>
   </si>
   <si>
-    <t>0.7103,0.0006,0.2749,0.0003</t>
-  </si>
-  <si>
-    <t>0.8726,0.0027,0.0907,0.0003</t>
-  </si>
-  <si>
-    <t>0.8879,0.0019,0.0710,0.0005</t>
+    <t>0.7101,0.0006,0.2754,0.0003</t>
+  </si>
+  <si>
+    <t>0.8722,0.0027,0.0910,0.0003</t>
+  </si>
+  <si>
+    <t>0.8877,0.0019,0.0712,0.0005</t>
   </si>
   <si>
     <t>0.0000,0.9986,0.9838,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0654,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0170,0.9972,0.0002</t>
+    <t>0.0002,0.0651,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0169,0.9972,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.9826,0.9701,0.0001</t>
@@ -1021,82 +1027,82 @@
     <t>0.0001,0.0003,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0127,0.9838,0.2441,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9997,0.0092,0.0000</t>
+    <t>0.0127,0.9838,0.2448,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0093,0.0000</t>
   </si>
   <si>
     <t>0.9862,0.0004,0.0149,0.0001</t>
   </si>
   <si>
-    <t>0.5334,0.0103,0.4722,0.0006</t>
+    <t>0.5333,0.0102,0.4726,0.0006</t>
   </si>
   <si>
     <t>0.0080,0.0027,0.9940,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.8198,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8882,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9585,0.0000</t>
+    <t>0.0001,0.8194,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8879,0.9950,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9586,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9839,0.9922,0.0000</t>
   </si>
   <si>
-    <t>0.0482,0.0030,0.0184,0.9838</t>
-  </si>
-  <si>
-    <t>0.0604,0.0011,0.0066,0.9767</t>
-  </si>
-  <si>
-    <t>0.1322,0.0007,0.0023,0.9505</t>
-  </si>
-  <si>
-    <t>0.0977,0.0031,0.0301,0.8776</t>
-  </si>
-  <si>
-    <t>0.5010,0.0041,0.0232,0.4712</t>
-  </si>
-  <si>
-    <t>0.0172,0.0066,0.0867,0.9729</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9751,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7361,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.7152,0.9813,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.3616,0.9975,0.0001</t>
+    <t>0.0482,0.0030,0.0185,0.9838</t>
+  </si>
+  <si>
+    <t>0.0605,0.0011,0.0067,0.9766</t>
+  </si>
+  <si>
+    <t>0.1323,0.0007,0.0023,0.9504</t>
+  </si>
+  <si>
+    <t>0.0974,0.0031,0.0302,0.8772</t>
+  </si>
+  <si>
+    <t>0.5011,0.0041,0.0232,0.4704</t>
+  </si>
+  <si>
+    <t>0.0172,0.0066,0.0868,0.9728</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9752,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7356,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.7145,0.9814,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.3607,0.9975,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9891,0.9970,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9518,0.9735,0.0000</t>
+    <t>0.0002,0.9517,0.9735,0.0000</t>
   </si>
   <si>
     <t>0.9736,0.0031,0.0126,0.0004</t>
   </si>
   <si>
-    <t>0.9115,0.0045,0.0631,0.0007</t>
+    <t>0.9115,0.0045,0.0632,0.0007</t>
   </si>
   <si>
     <t>0.9799,0.0080,0.0070,0.0005</t>
   </si>
   <si>
-    <t>0.9746,0.0025,0.0147,0.0004</t>
-  </si>
-  <si>
-    <t>0.9548,0.0017,0.0313,0.0006</t>
+    <t>0.9745,0.0025,0.0147,0.0004</t>
+  </si>
+  <si>
+    <t>0.9548,0.0016,0.0314,0.0006</t>
   </si>
   <si>
     <t>0.9657,0.0020,0.0163,0.0002</t>
@@ -1108,19 +1114,19 @@
     <t>0.9708,0.0026,0.0106,0.0000</t>
   </si>
   <si>
-    <t>0.9198,0.0007,0.0495,0.0003</t>
+    <t>0.9198,0.0007,0.0496,0.0003</t>
   </si>
   <si>
     <t>0.9718,0.0034,0.0136,0.0003</t>
   </si>
   <si>
-    <t>0.9651,0.0012,0.0252,0.0003</t>
+    <t>0.9650,0.0012,0.0252,0.0003</t>
   </si>
   <si>
     <t>0.9786,0.0017,0.0092,0.0002</t>
   </si>
   <si>
-    <t>0.9137,0.0034,0.0468,0.0008</t>
+    <t>0.9136,0.0034,0.0469,0.0008</t>
   </si>
   <si>
     <t>0.9920,0.0015,0.0029,0.0001</t>
@@ -1129,7 +1135,7 @@
     <t>0.9743,0.0023,0.0111,0.0003</t>
   </si>
   <si>
-    <t>0.8741,0.0017,0.0797,0.0009</t>
+    <t>0.8738,0.0017,0.0799,0.0009</t>
   </si>
   <si>
     <t>0.0025,0.0001,0.9991,0.0000</t>
@@ -1141,67 +1147,67 @@
     <t>0.9951,0.0001,0.0043,0.0000</t>
   </si>
   <si>
-    <t>0.2779,0.0007,0.8353,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.9958,0.2778,0.0005</t>
-  </si>
-  <si>
-    <t>0.0177,0.9937,0.0495,0.0002</t>
-  </si>
-  <si>
-    <t>0.9211,0.1392,0.0086,0.0013</t>
-  </si>
-  <si>
-    <t>0.7155,0.3014,0.0587,0.0047</t>
-  </si>
-  <si>
-    <t>0.0280,0.9818,0.1510,0.0017</t>
-  </si>
-  <si>
-    <t>0.0008,0.9995,0.1778,0.0001</t>
-  </si>
-  <si>
-    <t>0.9111,0.0429,0.0350,0.0025</t>
-  </si>
-  <si>
-    <t>0.5561,0.0181,0.4406,0.0015</t>
-  </si>
-  <si>
-    <t>0.1827,0.0067,0.8442,0.0004</t>
-  </si>
-  <si>
-    <t>0.8647,0.0061,0.1391,0.0005</t>
-  </si>
-  <si>
-    <t>0.7460,0.0130,0.2698,0.0015</t>
-  </si>
-  <si>
-    <t>0.0006,0.6866,0.9298,0.0194</t>
-  </si>
-  <si>
-    <t>0.0012,0.9995,0.1046,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9998,0.0440,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.9944,0.1271,0.0102</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.8003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0316,0.9479,0.2865,0.0012</t>
-  </si>
-  <si>
-    <t>0.8103,0.0544,0.0862,0.0046</t>
-  </si>
-  <si>
-    <t>0.7647,0.1510,0.0805,0.0150</t>
-  </si>
-  <si>
-    <t>0.9883,0.0004,0.0060,0.0001</t>
+    <t>0.2780,0.0007,0.8354,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.9958,0.2784,0.0005</t>
+  </si>
+  <si>
+    <t>0.0177,0.9937,0.0496,0.0002</t>
+  </si>
+  <si>
+    <t>0.9212,0.1389,0.0086,0.0013</t>
+  </si>
+  <si>
+    <t>0.7158,0.3008,0.0588,0.0047</t>
+  </si>
+  <si>
+    <t>0.0280,0.9818,0.1514,0.0017</t>
+  </si>
+  <si>
+    <t>0.0008,0.9995,0.1784,0.0001</t>
+  </si>
+  <si>
+    <t>0.9111,0.0429,0.0351,0.0025</t>
+  </si>
+  <si>
+    <t>0.5556,0.0181,0.4414,0.0015</t>
+  </si>
+  <si>
+    <t>0.1826,0.0066,0.8444,0.0004</t>
+  </si>
+  <si>
+    <t>0.8644,0.0060,0.1394,0.0005</t>
+  </si>
+  <si>
+    <t>0.7455,0.0130,0.2705,0.0015</t>
+  </si>
+  <si>
+    <t>0.0006,0.6863,0.9300,0.0194</t>
+  </si>
+  <si>
+    <t>0.0012,0.9995,0.1049,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9998,0.0441,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.9944,0.1276,0.0102</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.8005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0316,0.9478,0.2868,0.0012</t>
+  </si>
+  <si>
+    <t>0.8103,0.0543,0.0863,0.0046</t>
+  </si>
+  <si>
+    <t>0.7649,0.1507,0.0805,0.0150</t>
+  </si>
+  <si>
+    <t>0.9883,0.0004,0.0061,0.0001</t>
   </si>
   <si>
     <t>0.9733,0.0063,0.0108,0.0021</t>
@@ -1210,76 +1216,76 @@
     <t>0.9685,0.0025,0.0189,0.0005</t>
   </si>
   <si>
-    <t>0.9544,0.0017,0.0322,0.0005</t>
+    <t>0.9543,0.0017,0.0323,0.0004</t>
   </si>
   <si>
     <t>0.9968,0.0006,0.0014,0.0001</t>
   </si>
   <si>
-    <t>0.9294,0.0023,0.0394,0.0006</t>
-  </si>
-  <si>
-    <t>0.8720,0.0012,0.1058,0.0004</t>
-  </si>
-  <si>
-    <t>0.8292,0.0010,0.1231,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.8759,0.9896,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.1593,0.9985,0.0000</t>
+    <t>0.9294,0.0023,0.0395,0.0006</t>
+  </si>
+  <si>
+    <t>0.8719,0.0012,0.1060,0.0004</t>
+  </si>
+  <si>
+    <t>0.8291,0.0010,0.1234,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.8756,0.9896,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.1588,0.9985,0.0000</t>
   </si>
   <si>
     <t>0.0002,0.0097,0.9995,0.0001</t>
   </si>
   <si>
-    <t>0.0095,0.0065,0.9904,0.0000</t>
+    <t>0.0096,0.0065,0.9904,0.0000</t>
   </si>
   <si>
     <t>0.9884,0.0007,0.0076,0.0001</t>
   </si>
   <si>
-    <t>0.9318,0.0145,0.0381,0.0009</t>
-  </si>
-  <si>
-    <t>0.4839,0.0003,0.7155,0.0001</t>
+    <t>0.9318,0.0145,0.0382,0.0009</t>
+  </si>
+  <si>
+    <t>0.4842,0.0003,0.7154,0.0001</t>
   </si>
   <si>
     <t>0.9781,0.0012,0.0176,0.0001</t>
   </si>
   <si>
-    <t>0.1621,0.0018,0.0342,0.6676</t>
-  </si>
-  <si>
-    <t>0.0008,0.0013,0.0303,0.9989</t>
+    <t>0.1621,0.0018,0.0343,0.6661</t>
+  </si>
+  <si>
+    <t>0.0008,0.0013,0.0304,0.9989</t>
   </si>
   <si>
     <t>0.0021,0.0010,0.0088,0.9988</t>
   </si>
   <si>
-    <t>0.2354,0.0011,0.0177,0.8117</t>
+    <t>0.2355,0.0011,0.0178,0.8110</t>
   </si>
   <si>
     <t>0.0000,0.9872,0.9919,0.0000</t>
   </si>
   <si>
-    <t>0.8552,0.0016,0.1153,0.0005</t>
-  </si>
-  <si>
-    <t>0.2842,0.3535,0.4643,0.0204</t>
+    <t>0.8550,0.0015,0.1156,0.0005</t>
+  </si>
+  <si>
+    <t>0.2845,0.3527,0.4645,0.0204</t>
   </si>
   <si>
     <t>0.9715,0.0010,0.0192,0.0003</t>
   </si>
   <si>
-    <t>0.2968,0.3007,0.4045,0.0071</t>
+    <t>0.2968,0.3001,0.4049,0.0071</t>
   </si>
   <si>
     <t>0.9896,0.0017,0.0046,0.0005</t>
   </si>
   <si>
-    <t>0.1801,0.0000,0.9420,0.0000</t>
+    <t>0.1799,0.0000,0.9421,0.0000</t>
   </si>
   <si>
     <t>0.0520,0.0000,0.9864,0.0000</t>
@@ -1288,40 +1294,40 @@
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.5645,0.0001,0.2780,0.0005</t>
-  </si>
-  <si>
-    <t>0.9104,0.0051,0.0563,0.0016</t>
-  </si>
-  <si>
-    <t>0.8647,0.0216,0.1114,0.0046</t>
+    <t>0.5642,0.0001,0.2784,0.0005</t>
+  </si>
+  <si>
+    <t>0.9104,0.0051,0.0564,0.0016</t>
+  </si>
+  <si>
+    <t>0.8646,0.0215,0.1116,0.0046</t>
   </si>
   <si>
     <t>0.9918,0.0008,0.0054,0.0001</t>
   </si>
   <si>
-    <t>0.9674,0.0065,0.0206,0.0015</t>
-  </si>
-  <si>
-    <t>0.8435,0.0758,0.0826,0.0062</t>
-  </si>
-  <si>
-    <t>0.9702,0.0045,0.0201,0.0004</t>
+    <t>0.9675,0.0065,0.0206,0.0015</t>
+  </si>
+  <si>
+    <t>0.8436,0.0757,0.0827,0.0062</t>
+  </si>
+  <si>
+    <t>0.9702,0.0045,0.0202,0.0004</t>
   </si>
   <si>
     <t>0.9798,0.0016,0.0176,0.0002</t>
   </si>
   <si>
-    <t>0.9798,0.0010,0.0155,0.0002</t>
+    <t>0.9798,0.0010,0.0156,0.0002</t>
   </si>
   <si>
     <t>0.9908,0.0021,0.0039,0.0002</t>
   </si>
   <si>
-    <t>0.9528,0.0015,0.0303,0.0006</t>
-  </si>
-  <si>
-    <t>0.7943,0.0005,0.1841,0.0005</t>
+    <t>0.9527,0.0015,0.0304,0.0006</t>
+  </si>
+  <si>
+    <t>0.7938,0.0005,0.1847,0.0005</t>
   </si>
   <si>
     <t>0.9872,0.0009,0.0092,0.0003</t>
@@ -1333,49 +1339,49 @@
     <t>0.9845,0.0011,0.0109,0.0003</t>
   </si>
   <si>
-    <t>0.8634,0.0005,0.1413,0.0004</t>
-  </si>
-  <si>
-    <t>0.9599,0.0379,0.0107,0.0038</t>
-  </si>
-  <si>
-    <t>0.8182,0.0884,0.0700,0.0136</t>
-  </si>
-  <si>
-    <t>0.9249,0.0225,0.0276,0.0110</t>
-  </si>
-  <si>
-    <t>0.7968,0.0052,0.1359,0.0003</t>
-  </si>
-  <si>
-    <t>0.9091,0.0103,0.0564,0.0017</t>
+    <t>0.8630,0.0005,0.1419,0.0004</t>
+  </si>
+  <si>
+    <t>0.9599,0.0378,0.0107,0.0038</t>
+  </si>
+  <si>
+    <t>0.8182,0.0882,0.0700,0.0136</t>
+  </si>
+  <si>
+    <t>0.9249,0.0225,0.0276,0.0109</t>
+  </si>
+  <si>
+    <t>0.7967,0.0052,0.1361,0.0003</t>
+  </si>
+  <si>
+    <t>0.9089,0.0103,0.0565,0.0017</t>
   </si>
   <si>
     <t>0.9663,0.0031,0.0215,0.0007</t>
   </si>
   <si>
-    <t>0.8726,0.0018,0.0942,0.0008</t>
-  </si>
-  <si>
-    <t>0.9191,0.0111,0.0593,0.0019</t>
+    <t>0.8724,0.0018,0.0945,0.0008</t>
+  </si>
+  <si>
+    <t>0.9192,0.0110,0.0593,0.0019</t>
   </si>
   <si>
     <t>0.0156,0.0011,0.9892,0.0000</t>
   </si>
   <si>
-    <t>0.9262,0.0063,0.0520,0.0009</t>
+    <t>0.9258,0.0063,0.0524,0.0009</t>
   </si>
   <si>
     <t>0.0002,0.0004,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0473,0.9980,0.0005</t>
+    <t>0.0006,0.0472,0.9980,0.0005</t>
   </si>
   <si>
     <t>0.0288,0.0027,0.9832,0.0008</t>
   </si>
   <si>
-    <t>0.0057,0.0452,0.9885,0.0002</t>
+    <t>0.0057,0.0451,0.9885,0.0002</t>
   </si>
   <si>
     <t>0.0012,0.0022,0.9988,0.0000</t>
@@ -1384,70 +1390,70 @@
     <t>0.0040,0.0001,0.9987,0.0000</t>
   </si>
   <si>
-    <t>0.0622,0.0007,0.9693,0.0000</t>
-  </si>
-  <si>
-    <t>0.6215,0.0027,0.4517,0.0001</t>
-  </si>
-  <si>
-    <t>0.7261,0.0013,0.3760,0.0001</t>
+    <t>0.0623,0.0007,0.9693,0.0000</t>
+  </si>
+  <si>
+    <t>0.6211,0.0027,0.4522,0.0001</t>
+  </si>
+  <si>
+    <t>0.7260,0.0013,0.3763,0.0001</t>
   </si>
   <si>
     <t>0.9598,0.0046,0.0263,0.0003</t>
   </si>
   <si>
-    <t>0.3944,0.0164,0.6307,0.0013</t>
-  </si>
-  <si>
-    <t>0.0821,0.0323,0.8871,0.0005</t>
-  </si>
-  <si>
-    <t>0.2614,0.0042,0.7848,0.0002</t>
-  </si>
-  <si>
-    <t>0.8583,0.0037,0.1694,0.0005</t>
-  </si>
-  <si>
-    <t>0.9077,0.0069,0.0739,0.0002</t>
-  </si>
-  <si>
-    <t>0.5182,0.4771,0.0684,0.0016</t>
-  </si>
-  <si>
-    <t>0.0918,0.7890,0.3855,0.0044</t>
-  </si>
-  <si>
-    <t>0.6217,0.1783,0.1880,0.0093</t>
-  </si>
-  <si>
-    <t>0.7887,0.0080,0.1568,0.0014</t>
-  </si>
-  <si>
-    <t>0.5279,0.0748,0.3015,0.0046</t>
-  </si>
-  <si>
-    <t>0.9512,0.0132,0.0187,0.0002</t>
+    <t>0.3939,0.0164,0.6313,0.0013</t>
+  </si>
+  <si>
+    <t>0.0819,0.0321,0.8875,0.0005</t>
+  </si>
+  <si>
+    <t>0.2613,0.0041,0.7850,0.0002</t>
+  </si>
+  <si>
+    <t>0.8580,0.0037,0.1699,0.0005</t>
+  </si>
+  <si>
+    <t>0.9078,0.0068,0.0739,0.0002</t>
+  </si>
+  <si>
+    <t>0.5182,0.4767,0.0685,0.0016</t>
+  </si>
+  <si>
+    <t>0.0919,0.7883,0.3858,0.0044</t>
+  </si>
+  <si>
+    <t>0.6213,0.1781,0.1883,0.0093</t>
+  </si>
+  <si>
+    <t>0.7882,0.0079,0.1573,0.0014</t>
+  </si>
+  <si>
+    <t>0.5278,0.0746,0.3017,0.0046</t>
+  </si>
+  <si>
+    <t>0.9512,0.0132,0.0188,0.0002</t>
   </si>
   <si>
     <t>0.9906,0.0008,0.0049,0.0001</t>
   </si>
   <si>
-    <t>0.9186,0.0089,0.0721,0.0012</t>
-  </si>
-  <si>
-    <t>0.4619,0.0044,0.6165,0.0011</t>
-  </si>
-  <si>
-    <t>0.9216,0.0029,0.0755,0.0008</t>
-  </si>
-  <si>
-    <t>0.0621,0.0010,0.9696,0.0002</t>
-  </si>
-  <si>
-    <t>0.3333,0.0013,0.7330,0.0000</t>
-  </si>
-  <si>
-    <t>0.2234,0.0048,0.7751,0.0000</t>
+    <t>0.9186,0.0089,0.0722,0.0012</t>
+  </si>
+  <si>
+    <t>0.4622,0.0044,0.6163,0.0011</t>
+  </si>
+  <si>
+    <t>0.9215,0.0029,0.0758,0.0008</t>
+  </si>
+  <si>
+    <t>0.0621,0.0010,0.9697,0.0002</t>
+  </si>
+  <si>
+    <t>0.3326,0.0013,0.7337,0.0000</t>
+  </si>
+  <si>
+    <t>0.2230,0.0048,0.7755,0.0000</t>
   </si>
   <si>
     <t>0.0020,0.0090,0.9970,0.0001</t>
@@ -1456,37 +1462,37 @@
     <t>0.0113,0.0021,0.9884,0.0000</t>
   </si>
   <si>
-    <t>0.8804,0.0002,0.0960,0.0002</t>
-  </si>
-  <si>
-    <t>0.9081,0.0075,0.0498,0.0017</t>
-  </si>
-  <si>
-    <t>0.9258,0.0042,0.0408,0.0010</t>
+    <t>0.8800,0.0002,0.0964,0.0002</t>
+  </si>
+  <si>
+    <t>0.9081,0.0074,0.0498,0.0016</t>
+  </si>
+  <si>
+    <t>0.9257,0.0042,0.0409,0.0010</t>
   </si>
   <si>
     <t>0.9883,0.0034,0.0049,0.0007</t>
   </si>
   <si>
-    <t>0.8732,0.0112,0.0753,0.0021</t>
-  </si>
-  <si>
-    <t>0.8838,0.0116,0.0604,0.0020</t>
-  </si>
-  <si>
-    <t>0.9608,0.0042,0.0180,0.0008</t>
-  </si>
-  <si>
-    <t>0.8856,0.0007,0.0743,0.0005</t>
+    <t>0.8732,0.0111,0.0753,0.0021</t>
+  </si>
+  <si>
+    <t>0.8836,0.0116,0.0606,0.0020</t>
+  </si>
+  <si>
+    <t>0.9608,0.0041,0.0180,0.0008</t>
+  </si>
+  <si>
+    <t>0.8853,0.0007,0.0746,0.0005</t>
   </si>
   <si>
     <t>0.0203,0.0038,0.9841,0.0004</t>
   </si>
   <si>
-    <t>0.1355,0.0154,0.8771,0.0008</t>
-  </si>
-  <si>
-    <t>0.6522,0.0055,0.3416,0.0028</t>
+    <t>0.1354,0.0153,0.8773,0.0008</t>
+  </si>
+  <si>
+    <t>0.6517,0.0055,0.3425,0.0028</t>
   </si>
   <si>
     <t>0.0008,0.0003,0.9995,0.0000</t>
@@ -1495,73 +1501,73 @@
     <t>0.0001,0.0014,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0047,0.0209,0.9923,0.0002</t>
+    <t>0.0047,0.0208,0.9923,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0315,0.0045,0.9742,0.0001</t>
+    <t>0.0315,0.0045,0.9743,0.0001</t>
   </si>
   <si>
     <t>0.0040,0.0040,0.9960,0.0001</t>
   </si>
   <si>
-    <t>0.3133,0.0101,0.7243,0.0011</t>
+    <t>0.3131,0.0100,0.7246,0.0011</t>
   </si>
   <si>
     <t>0.9673,0.0009,0.0341,0.0001</t>
   </si>
   <si>
-    <t>0.9271,0.0006,0.0727,0.0004</t>
+    <t>0.9270,0.0006,0.0730,0.0004</t>
   </si>
   <si>
     <t>0.9903,0.0009,0.0051,0.0000</t>
   </si>
   <si>
-    <t>0.9415,0.0014,0.0451,0.0006</t>
+    <t>0.9414,0.0014,0.0453,0.0006</t>
   </si>
   <si>
     <t>0.9839,0.0045,0.0070,0.0006</t>
   </si>
   <si>
-    <t>0.9582,0.0027,0.0264,0.0006</t>
-  </si>
-  <si>
-    <t>0.8997,0.0065,0.0735,0.0014</t>
-  </si>
-  <si>
-    <t>0.8786,0.0009,0.0793,0.0007</t>
-  </si>
-  <si>
-    <t>0.9585,0.0046,0.0242,0.0009</t>
-  </si>
-  <si>
-    <t>0.9748,0.0023,0.0143,0.0004</t>
-  </si>
-  <si>
-    <t>0.8313,0.0036,0.0902,0.0009</t>
-  </si>
-  <si>
-    <t>0.0178,0.0180,0.9765,0.0002</t>
+    <t>0.9581,0.0027,0.0266,0.0006</t>
+  </si>
+  <si>
+    <t>0.8993,0.0065,0.0740,0.0014</t>
+  </si>
+  <si>
+    <t>0.8785,0.0009,0.0795,0.0007</t>
+  </si>
+  <si>
+    <t>0.9584,0.0046,0.0243,0.0009</t>
+  </si>
+  <si>
+    <t>0.9748,0.0022,0.0143,0.0004</t>
+  </si>
+  <si>
+    <t>0.8310,0.0036,0.0904,0.0009</t>
+  </si>
+  <si>
+    <t>0.0178,0.0180,0.9766,0.0002</t>
   </si>
   <si>
     <t>0.0010,0.0032,0.9989,0.0000</t>
   </si>
   <si>
-    <t>0.0016,0.0021,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0496,0.0122,0.9489,0.0003</t>
+    <t>0.0016,0.0020,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0496,0.0121,0.9490,0.0003</t>
   </si>
   <si>
     <t>0.0313,0.0008,0.9829,0.0000</t>
   </si>
   <si>
-    <t>0.8522,0.0082,0.1378,0.0012</t>
-  </si>
-  <si>
-    <t>0.1199,0.0110,0.8893,0.0015</t>
+    <t>0.8519,0.0081,0.1382,0.0012</t>
+  </si>
+  <si>
+    <t>0.1198,0.0110,0.8895,0.0015</t>
   </si>
   <si>
     <t>0.0007,0.0007,0.9994,0.0001</t>
@@ -1570,19 +1576,19 @@
     <t>0.9897,0.0009,0.0032,0.0007</t>
   </si>
   <si>
-    <t>0.0241,0.0018,0.0017,0.9945</t>
-  </si>
-  <si>
-    <t>0.4211,0.0014,0.0060,0.6372</t>
-  </si>
-  <si>
-    <t>0.0060,0.0003,0.0213,0.9963</t>
-  </si>
-  <si>
-    <t>0.0035,0.0010,0.0138,0.9978</t>
-  </si>
-  <si>
-    <t>0.9352,0.0093,0.0123,0.0165</t>
+    <t>0.0242,0.0018,0.0017,0.9944</t>
+  </si>
+  <si>
+    <t>0.4217,0.0014,0.0060,0.6361</t>
+  </si>
+  <si>
+    <t>0.0060,0.0003,0.0214,0.9962</t>
+  </si>
+  <si>
+    <t>0.0035,0.0010,0.0139,0.9978</t>
+  </si>
+  <si>
+    <t>0.9354,0.0093,0.0123,0.0164</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +1974,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1982,7 +1988,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,7 +2002,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,7 +2016,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,7 +2030,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2038,7 +2044,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2052,7 +2058,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,7 +2072,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2080,7 +2086,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2094,7 +2100,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2108,7 +2114,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2122,7 +2128,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2136,7 +2142,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,7 +2156,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,7 +2170,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,7 +2184,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2192,7 +2198,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,7 +2212,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,7 +2226,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,7 +2240,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,7 +2254,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,7 +2268,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2276,7 +2282,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2287,10 +2293,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,7 +2310,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,7 +2324,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,7 +2338,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,7 +2352,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,7 +2366,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2374,7 +2380,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,7 +2394,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,7 +2408,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,7 +2422,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2430,7 +2436,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2444,7 +2450,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,7 +2464,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2469,10 +2475,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,7 +2492,7 @@
         <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,7 +2506,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,7 +2520,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,7 +2534,7 @@
         <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,7 +2548,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,7 +2562,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,7 +2576,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,7 +2590,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,7 +2604,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,7 +2618,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,7 +2632,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,7 +2646,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,7 +2660,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,7 +2674,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,7 +2688,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,7 +2702,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,7 +2716,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,7 +2730,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2738,7 +2744,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2752,7 +2758,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,7 +2772,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2780,7 +2786,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2794,7 +2800,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,7 +2814,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2819,10 +2825,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,7 +2842,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,7 +2856,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2861,10 +2867,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,7 +2884,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,7 +2898,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,7 +2912,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2920,7 +2926,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,7 +2940,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,7 +2954,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2959,10 +2965,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2973,10 +2979,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2987,10 +2993,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3001,10 +3007,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3018,7 +3024,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3032,7 +3038,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3046,7 +3052,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3060,7 +3066,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3074,7 +3080,7 @@
         <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,7 +3094,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3099,10 +3105,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3113,10 +3119,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3127,10 +3133,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,7 +3150,7 @@
         <v>266</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3155,10 +3161,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3169,10 +3175,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,7 +3192,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,7 +3206,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3214,7 +3220,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3228,7 +3234,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3242,7 +3248,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3256,7 +3262,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3270,7 +3276,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3284,7 +3290,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3298,7 +3304,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3312,7 +3318,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3326,7 +3332,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3340,7 +3346,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3354,7 +3360,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3368,7 +3374,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,7 +3388,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,7 +3402,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,7 +3416,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,7 +3430,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3438,7 +3444,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,7 +3458,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,7 +3472,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,7 +3486,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,7 +3500,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,7 +3514,7 @@
         <v>264</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,7 +3528,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,7 +3542,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3550,7 +3556,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,7 +3570,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,7 +3584,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3592,7 +3598,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,7 +3612,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3617,10 +3623,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,7 +3640,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,7 +3654,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,7 +3668,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3673,10 +3679,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,7 +3696,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,7 +3710,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,7 +3724,7 @@
         <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3732,7 +3738,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3746,7 +3752,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,7 +3766,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3774,7 +3780,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3788,7 +3794,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,7 +3808,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3816,7 +3822,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3830,7 +3836,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3841,10 +3847,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,7 +3864,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,7 +3878,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,7 +3892,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3900,7 +3906,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,7 +3920,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3928,7 +3934,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3942,7 +3948,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3956,7 +3962,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,7 +3976,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,7 +3990,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3998,7 +4004,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4009,10 +4015,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4026,7 +4032,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4037,10 +4043,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,7 +4060,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4065,10 +4071,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4082,7 +4088,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,7 +4102,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,7 +4116,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,7 +4130,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4138,7 +4144,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4152,7 +4158,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,7 +4172,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4180,7 +4186,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4194,7 +4200,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,7 +4214,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4222,7 +4228,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4236,7 +4242,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,7 +4256,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4264,7 +4270,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4278,7 +4284,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4292,7 +4298,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4306,7 +4312,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,7 +4326,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4334,7 +4340,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4348,7 +4354,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,7 +4368,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,7 +4382,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,7 +4396,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4404,7 +4410,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,7 +4424,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,7 +4438,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4446,7 +4452,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4460,7 +4466,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,7 +4480,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,7 +4494,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,7 +4508,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,7 +4522,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,7 +4536,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,7 +4550,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,7 +4564,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,7 +4578,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,7 +4592,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,7 +4606,7 @@
         <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,7 +4620,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4628,7 +4634,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,7 +4648,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,7 +4662,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,7 +4676,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4684,7 +4690,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,7 +4704,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,7 +4718,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,7 +4732,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,7 +4746,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4754,7 +4760,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,7 +4774,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,7 +4788,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4796,7 +4802,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4810,7 +4816,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,7 +4830,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,7 +4844,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,7 +4858,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,7 +4872,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,7 +4886,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,7 +4900,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,7 +4914,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,7 +4928,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4936,7 +4942,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4950,7 +4956,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4964,7 +4970,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4978,7 +4984,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4992,7 +4998,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5006,7 +5012,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,7 +5026,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,7 +5040,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,7 +5054,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,7 +5068,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,7 +5082,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,7 +5096,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,7 +5110,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,7 +5124,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,7 +5138,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,7 +5152,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,7 +5166,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,7 +5180,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5188,7 +5194,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5202,7 +5208,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5216,7 +5222,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5230,7 +5236,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,7 +5250,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5258,7 +5264,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5272,7 +5278,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,7 +5292,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5300,7 +5306,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5314,7 +5320,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5328,7 +5334,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,7 +5348,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,7 +5362,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,7 +5376,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,7 +5390,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,7 +5404,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5412,7 +5418,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,7 +5432,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,7 +5446,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,7 +5460,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5468,7 +5474,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5482,7 +5488,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5496,7 +5502,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,7 +5516,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5524,7 +5530,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
